--- a/e2e/expectedData/sub_Master_Potongan_Homestaff.xlsx
+++ b/e2e/expectedData/sub_Master_Potongan_Homestaff.xlsx
@@ -221,7 +221,7 @@
     <t>8,10</t>
   </si>
   <si>
-    <t>DILI, 26 AGUSTUS 2026</t>
+    <t>DILI, 09 SEPTEMBER 2026</t>
   </si>
   <si>
     <t>Human Resource</t>

--- a/e2e/expectedData/sub_Master_Potongan_Homestaff.xlsx
+++ b/e2e/expectedData/sub_Master_Potongan_Homestaff.xlsx
@@ -221,7 +221,7 @@
     <t>8,10</t>
   </si>
   <si>
-    <t>DILI, 09 SEPTEMBER 2026</t>
+    <t>DILI, 10 SEPTEMBER 2026</t>
   </si>
   <si>
     <t>Human Resource</t>
